--- a/order_forms/034_gym_custom_wall_mirror_installation_order_form--order_forms.xlsx
+++ b/order_forms/034_gym_custom_wall_mirror_installation_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'small',_'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'small', 'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'large',_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'large', 'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'metal',_'label':_'metal'}</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'metal', 'label': 'Metal'}</t>
+          <t>Metal</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'glass',_'label':_'glass'}</t>
+          <t>glass</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'glass', 'label': 'Glass'}</t>
+          <t>Glass</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'frame',_'label':_'frame'}</t>
+          <t>frame</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'frame', 'label': 'Frame'}</t>
+          <t>Frame</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'frameless',_'label':_'frameless'}</t>
+          <t>frameless</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'frameless', 'label': 'Frameless'}</t>
+          <t>Frameless</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'screw',_'label':_'screw'}</t>
+          <t>screw</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'screw', 'label': 'Screw'}</t>
+          <t>Screw</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'adhesive',_'label':_'adhesive'}</t>
+          <t>adhesive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'adhesive', 'label': 'Adhesive'}</t>
+          <t>Adhesive</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'matte-finish',_'label':_'matte_finish'}</t>
+          <t>matte_finish</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'matte-finish', 'label': 'Matte Finish'}</t>
+          <t>Matte Finish</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'glossy-finish',_'label':_'glossy_finish'}</t>
+          <t>glossy_finish</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'glossy-finish', 'label': 'Glossy Finish'}</t>
+          <t>Glossy Finish</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'white',_'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'white', 'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'silver',_'label':_'silver'}</t>
+          <t>silver</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'silver', 'label': 'Silver'}</t>
+          <t>Silver</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'no-pattern',_'label':_'no_pattern'}</t>
+          <t>no_pattern</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'no-pattern', 'label': 'No Pattern'}</t>
+          <t>No Pattern</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'wood-grain',_'label':_'wood_grain'}</t>
+          <t>wood_grain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'wood-grain', 'label': 'Wood Grain'}</t>
+          <t>Wood Grain</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'etched-design',_'label':_'etched_design'}</t>
+          <t>etched_design</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'etched-design', 'label': 'Etched Design'}</t>
+          <t>Etched Design</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'portrait',_'label':_'portrait'}</t>
+          <t>portrait</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'portrait', 'label': 'Portrait'}</t>
+          <t>Portrait</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'landscape',_'label':_'landscape'}</t>
+          <t>landscape</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'landscape', 'label': 'Landscape'}</t>
+          <t>Landscape</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'drywall',_'label':_'drywall'}</t>
+          <t>drywall</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'drywall', 'label': 'Drywall'}</t>
+          <t>Drywall</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'concrete',_'label':_'concrete'}</t>
+          <t>concrete</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'concrete', 'label': 'Concrete'}</t>
+          <t>Concrete</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'ground',_'label':_'ground'}</t>
+          <t>ground</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'ground', 'label': 'Ground'}</t>
+          <t>Ground</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'freight',_'label':_'freight'}</t>
+          <t>freight</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'freight', 'label': 'Freight'}</t>
+          <t>Freight</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'credit-card',_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'credit-card', 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'bank-transfer',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'bank-transfer', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
